--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222306</v>
+        <v>122222260</v>
       </c>
       <c r="B8" t="n">
         <v>98175</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571205</v>
+        <v>571242</v>
       </c>
       <c r="R8" t="n">
-        <v>6507459</v>
+        <v>6507395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222191</v>
+        <v>122222306</v>
       </c>
       <c r="B9" t="n">
         <v>98175</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571216</v>
+        <v>571205</v>
       </c>
       <c r="R9" t="n">
-        <v>6507246</v>
+        <v>6507459</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222260</v>
+        <v>122222209</v>
       </c>
       <c r="B11" t="n">
         <v>98175</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571242</v>
+        <v>571189</v>
       </c>
       <c r="R11" t="n">
-        <v>6507395</v>
+        <v>6507243</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222209</v>
+        <v>122222191</v>
       </c>
       <c r="B12" t="n">
         <v>98175</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571189</v>
+        <v>571216</v>
       </c>
       <c r="R12" t="n">
-        <v>6507243</v>
+        <v>6507246</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273718</v>
+        <v>122273731</v>
       </c>
       <c r="B14" t="n">
-        <v>95722</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571268</v>
+        <v>571191</v>
       </c>
       <c r="R14" t="n">
-        <v>6507430</v>
+        <v>6507391</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273727</v>
+        <v>122273722</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>8436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,50 +2148,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571200</v>
+        <v>571231</v>
       </c>
       <c r="R15" t="n">
-        <v>6507458</v>
+        <v>6507251</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2232,7 +2220,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273721</v>
+        <v>122273718</v>
       </c>
       <c r="B16" t="n">
-        <v>90799</v>
+        <v>95722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2291,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571172</v>
+        <v>571268</v>
       </c>
       <c r="R16" t="n">
-        <v>6507239</v>
+        <v>6507430</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2353,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273731</v>
+        <v>122273721</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>90799</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,25 +2352,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571191</v>
+        <v>571172</v>
       </c>
       <c r="R17" t="n">
-        <v>6507391</v>
+        <v>6507239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2557,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273726</v>
+        <v>122273716</v>
       </c>
       <c r="B19" t="n">
-        <v>95764</v>
+        <v>95722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571267</v>
+        <v>571230</v>
       </c>
       <c r="R19" t="n">
-        <v>6507269</v>
+        <v>6507422</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2761,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273722</v>
+        <v>122273727</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>98175</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,38 +2760,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571231</v>
+        <v>571200</v>
       </c>
       <c r="R21" t="n">
-        <v>6507251</v>
+        <v>6507458</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2845,6 +2844,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273728</v>
+        <v>122273726</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>95764</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571196</v>
+        <v>571267</v>
       </c>
       <c r="R22" t="n">
-        <v>6507330</v>
+        <v>6507269</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273716</v>
+        <v>122273728</v>
       </c>
       <c r="B23" t="n">
-        <v>95722</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,25 +2977,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>5420</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571230</v>
+        <v>571196</v>
       </c>
       <c r="R23" t="n">
-        <v>6507422</v>
+        <v>6507330</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282433</v>
+        <v>122282755</v>
       </c>
       <c r="B25" t="n">
-        <v>94840</v>
+        <v>95722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,25 +3191,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3219,13 +3219,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571196</v>
+        <v>571260</v>
       </c>
       <c r="R25" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282549</v>
+        <v>122282656</v>
       </c>
       <c r="B26" t="n">
-        <v>95722</v>
+        <v>94840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571228</v>
+        <v>571260</v>
       </c>
       <c r="R26" t="n">
-        <v>6507441</v>
+        <v>6507444</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282429</v>
+        <v>122282513</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
+        <v>98175</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3395,31 +3395,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3428,13 +3432,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571198</v>
+        <v>571238</v>
       </c>
       <c r="R27" t="n">
-        <v>6507329</v>
+        <v>6507409</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3478,22 +3482,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282513</v>
+        <v>122282433</v>
       </c>
       <c r="B28" t="n">
-        <v>98175</v>
+        <v>94840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,47 +3506,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571238</v>
+        <v>571196</v>
       </c>
       <c r="R28" t="n">
-        <v>6507409</v>
+        <v>6507329</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3589,19 +3584,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282755</v>
+        <v>122282549</v>
       </c>
       <c r="B29" t="n">
         <v>95722</v>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571260</v>
+        <v>571228</v>
       </c>
       <c r="R29" t="n">
-        <v>6507444</v>
+        <v>6507441</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3703,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282656</v>
+        <v>122282429</v>
       </c>
       <c r="B30" t="n">
-        <v>94840</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3719,34 +3714,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571260</v>
+        <v>571198</v>
       </c>
       <c r="R30" t="n">
-        <v>6507444</v>
+        <v>6507329</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B31" t="n">
         <v>57527</v>
@@ -3838,29 +3838,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R31" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,19 +3899,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B32" t="n">
         <v>57527</v>
@@ -3952,21 +3944,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R32" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222260</v>
+        <v>122222191</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571242</v>
+        <v>571216</v>
       </c>
       <c r="R8" t="n">
-        <v>6507395</v>
+        <v>6507246</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222306</v>
+        <v>122222260</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571205</v>
+        <v>571242</v>
       </c>
       <c r="R9" t="n">
-        <v>6507459</v>
+        <v>6507395</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222234</v>
+        <v>122222209</v>
       </c>
       <c r="B10" t="n">
-        <v>105280</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1612,14 +1612,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571224</v>
+        <v>571189</v>
       </c>
       <c r="R10" t="n">
-        <v>6507389</v>
+        <v>6507243</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222209</v>
+        <v>122222234</v>
       </c>
       <c r="B11" t="n">
-        <v>98175</v>
+        <v>105290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,35 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571189</v>
+        <v>571224</v>
       </c>
       <c r="R11" t="n">
-        <v>6507243</v>
+        <v>6507389</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222191</v>
+        <v>122222306</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571216</v>
+        <v>571205</v>
       </c>
       <c r="R12" t="n">
-        <v>6507246</v>
+        <v>6507459</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,7 +1935,7 @@
         <v>122273720</v>
       </c>
       <c r="B13" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273731</v>
+        <v>122273718</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>95732</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571191</v>
+        <v>571268</v>
       </c>
       <c r="R14" t="n">
-        <v>6507391</v>
+        <v>6507430</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273722</v>
+        <v>122273728</v>
       </c>
       <c r="B15" t="n">
-        <v>8436</v>
+        <v>91194</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571231</v>
+        <v>571196</v>
       </c>
       <c r="R15" t="n">
-        <v>6507251</v>
+        <v>6507330</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273718</v>
+        <v>122273731</v>
       </c>
       <c r="B16" t="n">
-        <v>95722</v>
+        <v>5173</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,25 +2250,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571268</v>
+        <v>571191</v>
       </c>
       <c r="R16" t="n">
-        <v>6507430</v>
+        <v>6507391</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273721</v>
+        <v>122273717</v>
       </c>
       <c r="B17" t="n">
-        <v>90799</v>
+        <v>95732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571172</v>
+        <v>571238</v>
       </c>
       <c r="R17" t="n">
-        <v>6507239</v>
+        <v>6507436</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273717</v>
+        <v>122273722</v>
       </c>
       <c r="B18" t="n">
-        <v>95722</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571238</v>
+        <v>571231</v>
       </c>
       <c r="R18" t="n">
-        <v>6507436</v>
+        <v>6507251</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273716</v>
+        <v>122273727</v>
       </c>
       <c r="B19" t="n">
-        <v>95722</v>
+        <v>98185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,38 +2556,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571230</v>
+        <v>571200</v>
       </c>
       <c r="R19" t="n">
-        <v>6507422</v>
+        <v>6507458</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2628,6 +2640,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2748,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273727</v>
+        <v>122273716</v>
       </c>
       <c r="B21" t="n">
-        <v>98175</v>
+        <v>95732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,50 +2773,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571200</v>
+        <v>571230</v>
       </c>
       <c r="R21" t="n">
-        <v>6507458</v>
+        <v>6507422</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2844,7 +2845,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273726</v>
+        <v>122273721</v>
       </c>
       <c r="B22" t="n">
-        <v>95764</v>
+        <v>90809</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,25 +2875,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571267</v>
+        <v>571172</v>
       </c>
       <c r="R22" t="n">
-        <v>6507269</v>
+        <v>6507239</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273728</v>
+        <v>122273726</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
+        <v>95774</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>2590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571196</v>
+        <v>571267</v>
       </c>
       <c r="R23" t="n">
-        <v>6507330</v>
+        <v>6507269</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282416</v>
+        <v>122282755</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>95732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,51 +3079,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571210</v>
+        <v>571260</v>
       </c>
       <c r="R24" t="n">
-        <v>6507290</v>
+        <v>6507444</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3179,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282755</v>
+        <v>122282416</v>
       </c>
       <c r="B25" t="n">
-        <v>95722</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,41 +3181,51 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R25" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282656</v>
+        <v>122282429</v>
       </c>
       <c r="B26" t="n">
-        <v>94840</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,34 +3297,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571260</v>
+        <v>571198</v>
       </c>
       <c r="R26" t="n">
-        <v>6507444</v>
+        <v>6507329</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3386,7 +3391,7 @@
         <v>122282513</v>
       </c>
       <c r="B27" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282433</v>
+        <v>122282656</v>
       </c>
       <c r="B28" t="n">
-        <v>94840</v>
+        <v>94850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,13 +3539,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571196</v>
+        <v>571260</v>
       </c>
       <c r="R28" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3596,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282549</v>
+        <v>122282433</v>
       </c>
       <c r="B29" t="n">
-        <v>95722</v>
+        <v>94850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3613,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,13 +3641,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571228</v>
+        <v>571196</v>
       </c>
       <c r="R29" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282429</v>
+        <v>122282549</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>95732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,43 +3715,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571198</v>
+        <v>571228</v>
       </c>
       <c r="R30" t="n">
-        <v>6507329</v>
+        <v>6507441</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1436,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222260</v>
+        <v>122222209</v>
       </c>
       <c r="B9" t="n">
         <v>98185</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571242</v>
+        <v>571189</v>
       </c>
       <c r="R9" t="n">
-        <v>6507395</v>
+        <v>6507243</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222209</v>
+        <v>122222234</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>105290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1612,14 +1612,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571189</v>
+        <v>571224</v>
       </c>
       <c r="R10" t="n">
-        <v>6507243</v>
+        <v>6507389</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222234</v>
+        <v>122222306</v>
       </c>
       <c r="B11" t="n">
-        <v>105290</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,35 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571224</v>
+        <v>571205</v>
       </c>
       <c r="R11" t="n">
-        <v>6507389</v>
+        <v>6507459</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222306</v>
+        <v>122222260</v>
       </c>
       <c r="B12" t="n">
         <v>98185</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571205</v>
+        <v>571242</v>
       </c>
       <c r="R12" t="n">
-        <v>6507459</v>
+        <v>6507395</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273718</v>
+        <v>122273716</v>
       </c>
       <c r="B14" t="n">
         <v>95732</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571268</v>
+        <v>571230</v>
       </c>
       <c r="R14" t="n">
-        <v>6507430</v>
+        <v>6507422</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273728</v>
+        <v>122273726</v>
       </c>
       <c r="B15" t="n">
-        <v>91194</v>
+        <v>95774</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571196</v>
+        <v>571267</v>
       </c>
       <c r="R15" t="n">
-        <v>6507330</v>
+        <v>6507269</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273731</v>
+        <v>122273730</v>
       </c>
       <c r="B16" t="n">
         <v>5173</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571191</v>
+        <v>571190</v>
       </c>
       <c r="R16" t="n">
-        <v>6507391</v>
+        <v>6507410</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273717</v>
+        <v>122273718</v>
       </c>
       <c r="B17" t="n">
         <v>95732</v>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571238</v>
+        <v>571268</v>
       </c>
       <c r="R17" t="n">
-        <v>6507436</v>
+        <v>6507430</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273727</v>
+        <v>122273717</v>
       </c>
       <c r="B19" t="n">
-        <v>98185</v>
+        <v>95732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,50 +2556,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571200</v>
+        <v>571238</v>
       </c>
       <c r="R19" t="n">
-        <v>6507458</v>
+        <v>6507436</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2640,7 +2628,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2659,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273730</v>
+        <v>122273721</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>90809</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,25 +2658,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571190</v>
+        <v>571172</v>
       </c>
       <c r="R20" t="n">
-        <v>6507410</v>
+        <v>6507239</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2761,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273716</v>
+        <v>122273728</v>
       </c>
       <c r="B21" t="n">
-        <v>95732</v>
+        <v>91194</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,25 +2760,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571230</v>
+        <v>571196</v>
       </c>
       <c r="R21" t="n">
-        <v>6507422</v>
+        <v>6507330</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2863,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273721</v>
+        <v>122273727</v>
       </c>
       <c r="B22" t="n">
-        <v>90809</v>
+        <v>98185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,38 +2862,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571172</v>
+        <v>571200</v>
       </c>
       <c r="R22" t="n">
-        <v>6507239</v>
+        <v>6507458</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2947,6 +2946,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273726</v>
+        <v>122273731</v>
       </c>
       <c r="B23" t="n">
-        <v>95774</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571267</v>
+        <v>571191</v>
       </c>
       <c r="R23" t="n">
-        <v>6507269</v>
+        <v>6507391</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282755</v>
+        <v>122282513</v>
       </c>
       <c r="B24" t="n">
-        <v>95732</v>
+        <v>98185</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,41 +3079,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571260</v>
+        <v>571238</v>
       </c>
       <c r="R24" t="n">
-        <v>6507444</v>
+        <v>6507409</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,22 +3166,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282416</v>
+        <v>122282549</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>95732</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3181,51 +3190,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571210</v>
+        <v>571228</v>
       </c>
       <c r="R25" t="n">
-        <v>6507290</v>
+        <v>6507441</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3281,10 +3280,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282429</v>
+        <v>122282433</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>94850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,42 +3296,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571198</v>
+        <v>571196</v>
       </c>
       <c r="R26" t="n">
         <v>6507329</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3388,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282513</v>
+        <v>122282656</v>
       </c>
       <c r="B27" t="n">
-        <v>98185</v>
+        <v>94850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,50 +3394,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571238</v>
+        <v>571260</v>
       </c>
       <c r="R27" t="n">
-        <v>6507409</v>
+        <v>6507444</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3487,22 +3472,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282656</v>
+        <v>122282755</v>
       </c>
       <c r="B28" t="n">
-        <v>94850</v>
+        <v>95732</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,25 +3496,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282433</v>
+        <v>122282416</v>
       </c>
       <c r="B29" t="n">
-        <v>94850</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,34 +3602,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571196</v>
+        <v>571210</v>
       </c>
       <c r="R29" t="n">
-        <v>6507329</v>
+        <v>6507290</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3703,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282549</v>
+        <v>122282429</v>
       </c>
       <c r="B30" t="n">
-        <v>95732</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,38 +3710,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571228</v>
+        <v>571198</v>
       </c>
       <c r="R30" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222191</v>
+        <v>122222234</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>105303</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,35 +1324,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571216</v>
+        <v>571224</v>
       </c>
       <c r="R8" t="n">
-        <v>6507246</v>
+        <v>6507389</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
         <v>122222209</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222234</v>
+        <v>122222306</v>
       </c>
       <c r="B10" t="n">
-        <v>105290</v>
+        <v>98197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1612,14 +1612,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571224</v>
+        <v>571205</v>
       </c>
       <c r="R10" t="n">
-        <v>6507389</v>
+        <v>6507459</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222306</v>
+        <v>122222260</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571205</v>
+        <v>571242</v>
       </c>
       <c r="R11" t="n">
-        <v>6507459</v>
+        <v>6507395</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222260</v>
+        <v>122222191</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571242</v>
+        <v>571216</v>
       </c>
       <c r="R12" t="n">
-        <v>6507395</v>
+        <v>6507246</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273720</v>
+        <v>122273731</v>
       </c>
       <c r="B13" t="n">
-        <v>90809</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571220</v>
+        <v>571191</v>
       </c>
       <c r="R13" t="n">
-        <v>6507422</v>
+        <v>6507391</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2037,7 +2037,7 @@
         <v>122273716</v>
       </c>
       <c r="B14" t="n">
-        <v>95732</v>
+        <v>95744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273726</v>
+        <v>122273727</v>
       </c>
       <c r="B15" t="n">
-        <v>95774</v>
+        <v>98197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,38 +2148,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571267</v>
+        <v>571200</v>
       </c>
       <c r="R15" t="n">
-        <v>6507269</v>
+        <v>6507458</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2220,6 +2232,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2343,7 +2356,7 @@
         <v>122273718</v>
       </c>
       <c r="B17" t="n">
-        <v>95732</v>
+        <v>95744</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,7 +2458,7 @@
         <v>122273722</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273717</v>
+        <v>122273726</v>
       </c>
       <c r="B19" t="n">
-        <v>95732</v>
+        <v>95786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,25 +2569,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571238</v>
+        <v>571267</v>
       </c>
       <c r="R19" t="n">
-        <v>6507436</v>
+        <v>6507269</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2649,7 +2662,7 @@
         <v>122273721</v>
       </c>
       <c r="B20" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273728</v>
+        <v>122273717</v>
       </c>
       <c r="B21" t="n">
-        <v>91194</v>
+        <v>95744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,25 +2773,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571196</v>
+        <v>571238</v>
       </c>
       <c r="R21" t="n">
-        <v>6507330</v>
+        <v>6507436</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2850,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273727</v>
+        <v>122273720</v>
       </c>
       <c r="B22" t="n">
-        <v>98185</v>
+        <v>90821</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,50 +2875,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571200</v>
+        <v>571220</v>
       </c>
       <c r="R22" t="n">
-        <v>6507458</v>
+        <v>6507422</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2946,7 +2947,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273731</v>
+        <v>122273728</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>91206</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571191</v>
+        <v>571196</v>
       </c>
       <c r="R23" t="n">
-        <v>6507391</v>
+        <v>6507330</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282513</v>
+        <v>122282416</v>
       </c>
       <c r="B24" t="n">
-        <v>98185</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,35 +3079,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3116,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571238</v>
+        <v>571210</v>
       </c>
       <c r="R24" t="n">
-        <v>6507409</v>
+        <v>6507290</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3166,22 +3167,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282549</v>
+        <v>122282656</v>
       </c>
       <c r="B25" t="n">
-        <v>95732</v>
+        <v>94862</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3190,25 +3191,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3219,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571228</v>
+        <v>571260</v>
       </c>
       <c r="R25" t="n">
-        <v>6507441</v>
+        <v>6507444</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3280,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282433</v>
+        <v>122282429</v>
       </c>
       <c r="B26" t="n">
-        <v>94850</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,37 +3297,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571196</v>
+        <v>571198</v>
       </c>
       <c r="R26" t="n">
         <v>6507329</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3382,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282656</v>
+        <v>122282513</v>
       </c>
       <c r="B27" t="n">
-        <v>94850</v>
+        <v>98197</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3394,41 +3400,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571260</v>
+        <v>571238</v>
       </c>
       <c r="R27" t="n">
-        <v>6507444</v>
+        <v>6507409</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3472,22 +3487,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282755</v>
+        <v>122282433</v>
       </c>
       <c r="B28" t="n">
-        <v>95732</v>
+        <v>94862</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3496,25 +3511,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3524,13 +3539,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571260</v>
+        <v>571196</v>
       </c>
       <c r="R28" t="n">
-        <v>6507444</v>
+        <v>6507329</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3586,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282416</v>
+        <v>122282549</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>95744</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3598,51 +3613,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571210</v>
+        <v>571228</v>
       </c>
       <c r="R29" t="n">
-        <v>6507290</v>
+        <v>6507441</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282429</v>
+        <v>122282755</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>95744</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,43 +3715,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571198</v>
+        <v>571260</v>
       </c>
       <c r="R30" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3805,10 +3805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B31" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3838,21 +3838,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R31" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,22 +3907,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B32" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3944,29 +3952,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R32" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222234</v>
+        <v>122222260</v>
       </c>
       <c r="B8" t="n">
-        <v>105303</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,35 +1324,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571224</v>
+        <v>571242</v>
       </c>
       <c r="R8" t="n">
-        <v>6507389</v>
+        <v>6507395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222209</v>
+        <v>122222191</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571189</v>
+        <v>571216</v>
       </c>
       <c r="R9" t="n">
-        <v>6507243</v>
+        <v>6507246</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1563,7 @@
         <v>122222306</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222260</v>
+        <v>122222234</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>105308</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,35 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571242</v>
+        <v>571224</v>
       </c>
       <c r="R11" t="n">
-        <v>6507395</v>
+        <v>6507389</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222191</v>
+        <v>122222209</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571216</v>
+        <v>571189</v>
       </c>
       <c r="R12" t="n">
-        <v>6507246</v>
+        <v>6507243</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273731</v>
+        <v>122273720</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>90828</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571191</v>
+        <v>571220</v>
       </c>
       <c r="R13" t="n">
-        <v>6507391</v>
+        <v>6507422</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273716</v>
+        <v>122273726</v>
       </c>
       <c r="B14" t="n">
-        <v>95744</v>
+        <v>95791</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571230</v>
+        <v>571267</v>
       </c>
       <c r="R14" t="n">
-        <v>6507422</v>
+        <v>6507269</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273727</v>
+        <v>122273722</v>
       </c>
       <c r="B15" t="n">
-        <v>98197</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,50 +2148,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571200</v>
+        <v>571231</v>
       </c>
       <c r="R15" t="n">
-        <v>6507458</v>
+        <v>6507251</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2232,7 +2220,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273730</v>
+        <v>122273721</v>
       </c>
       <c r="B16" t="n">
-        <v>5173</v>
+        <v>90828</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,25 +2250,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2291,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571190</v>
+        <v>571172</v>
       </c>
       <c r="R16" t="n">
-        <v>6507410</v>
+        <v>6507239</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2353,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273718</v>
+        <v>122273730</v>
       </c>
       <c r="B17" t="n">
-        <v>95744</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,25 +2352,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571268</v>
+        <v>571190</v>
       </c>
       <c r="R17" t="n">
-        <v>6507430</v>
+        <v>6507410</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2455,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273722</v>
+        <v>122273716</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>95749</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571231</v>
+        <v>571230</v>
       </c>
       <c r="R18" t="n">
-        <v>6507251</v>
+        <v>6507422</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2557,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273726</v>
+        <v>122273717</v>
       </c>
       <c r="B19" t="n">
-        <v>95786</v>
+        <v>95749</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571267</v>
+        <v>571238</v>
       </c>
       <c r="R19" t="n">
-        <v>6507269</v>
+        <v>6507436</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2659,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273721</v>
+        <v>122273731</v>
       </c>
       <c r="B20" t="n">
-        <v>90821</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,25 +2658,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571172</v>
+        <v>571191</v>
       </c>
       <c r="R20" t="n">
-        <v>6507239</v>
+        <v>6507391</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2761,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273717</v>
+        <v>122273728</v>
       </c>
       <c r="B21" t="n">
-        <v>95744</v>
+        <v>91211</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,25 +2760,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571238</v>
+        <v>571196</v>
       </c>
       <c r="R21" t="n">
-        <v>6507436</v>
+        <v>6507330</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2863,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273720</v>
+        <v>122273727</v>
       </c>
       <c r="B22" t="n">
-        <v>90821</v>
+        <v>98202</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,38 +2862,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571220</v>
+        <v>571200</v>
       </c>
       <c r="R22" t="n">
-        <v>6507422</v>
+        <v>6507458</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2947,6 +2946,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273728</v>
+        <v>122273718</v>
       </c>
       <c r="B23" t="n">
-        <v>91206</v>
+        <v>95749</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,25 +2977,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571196</v>
+        <v>571268</v>
       </c>
       <c r="R23" t="n">
-        <v>6507330</v>
+        <v>6507430</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282416</v>
+        <v>122282656</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>94867</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,47 +3083,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571210</v>
+        <v>571260</v>
       </c>
       <c r="R24" t="n">
-        <v>6507290</v>
+        <v>6507444</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3179,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282656</v>
+        <v>122282429</v>
       </c>
       <c r="B25" t="n">
-        <v>94862</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3195,34 +3185,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571260</v>
+        <v>571198</v>
       </c>
       <c r="R25" t="n">
-        <v>6507444</v>
+        <v>6507329</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3281,7 +3276,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282429</v>
+        <v>122282416</v>
       </c>
       <c r="B26" t="n">
         <v>5173</v>
@@ -3315,9 +3310,14 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571198</v>
+        <v>571210</v>
       </c>
       <c r="R26" t="n">
-        <v>6507329</v>
+        <v>6507290</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>122282513</v>
       </c>
       <c r="B27" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282433</v>
+        <v>122282755</v>
       </c>
       <c r="B28" t="n">
-        <v>94862</v>
+        <v>95749</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,25 +3511,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571196</v>
+        <v>571260</v>
       </c>
       <c r="R28" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282549</v>
+        <v>122282433</v>
       </c>
       <c r="B29" t="n">
-        <v>95744</v>
+        <v>94867</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3613,25 +3613,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571228</v>
+        <v>571196</v>
       </c>
       <c r="R29" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282755</v>
+        <v>122282549</v>
       </c>
       <c r="B30" t="n">
-        <v>95744</v>
+        <v>95749</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571260</v>
+        <v>571228</v>
       </c>
       <c r="R30" t="n">
-        <v>6507444</v>
+        <v>6507441</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222260</v>
+        <v>122222306</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,11 +1330,6 @@
       <c r="E8" t="n">
         <v>220787</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1347,7 +1342,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,14 +1359,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571242</v>
+        <v>571205</v>
       </c>
       <c r="R8" t="n">
-        <v>6507395</v>
+        <v>6507459</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222191</v>
+        <v>122222209</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,11 +1449,6 @@
       <c r="E9" t="n">
         <v>220787</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1471,7 +1461,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1478,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571216</v>
+        <v>571189</v>
       </c>
       <c r="R9" t="n">
-        <v>6507246</v>
+        <v>6507243</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222306</v>
+        <v>122222191</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,11 +1568,6 @@
       <c r="E10" t="n">
         <v>220787</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1595,7 +1580,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1612,14 +1597,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571205</v>
+        <v>571216</v>
       </c>
       <c r="R10" t="n">
-        <v>6507459</v>
+        <v>6507246</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1687,7 +1672,7 @@
         <v>122222234</v>
       </c>
       <c r="B11" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,11 +1686,6 @@
       </c>
       <c r="E11" t="n">
         <v>221144</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1808,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222209</v>
+        <v>122222260</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,11 +1806,6 @@
       <c r="E12" t="n">
         <v>220787</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1843,7 +1818,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1835,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571189</v>
+        <v>571242</v>
       </c>
       <c r="R12" t="n">
-        <v>6507243</v>
+        <v>6507395</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1932,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273720</v>
+        <v>122273716</v>
       </c>
       <c r="B13" t="n">
-        <v>90828</v>
+        <v>95758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1923,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,7 +1942,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571220</v>
+        <v>571230</v>
       </c>
       <c r="R13" t="n">
         <v>6507422</v>
@@ -2034,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273726</v>
+        <v>122273731</v>
       </c>
       <c r="B14" t="n">
-        <v>95791</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2020,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Kornknutmossa</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571267</v>
+        <v>571191</v>
       </c>
       <c r="R14" t="n">
-        <v>6507269</v>
+        <v>6507391</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273722</v>
+        <v>122273730</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2117,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571231</v>
+        <v>571190</v>
       </c>
       <c r="R15" t="n">
-        <v>6507251</v>
+        <v>6507410</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273721</v>
+        <v>122273718</v>
       </c>
       <c r="B16" t="n">
-        <v>90828</v>
+        <v>95758</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,21 +2214,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571172</v>
+        <v>571268</v>
       </c>
       <c r="R16" t="n">
-        <v>6507239</v>
+        <v>6507430</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273730</v>
+        <v>122273717</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>95758</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,25 +2307,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571190</v>
+        <v>571238</v>
       </c>
       <c r="R17" t="n">
-        <v>6507410</v>
+        <v>6507436</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2442,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273716</v>
+        <v>122273728</v>
       </c>
       <c r="B18" t="n">
-        <v>95749</v>
+        <v>91216</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,25 +2404,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>5420</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571230</v>
+        <v>571196</v>
       </c>
       <c r="R18" t="n">
-        <v>6507422</v>
+        <v>6507330</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2544,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273717</v>
+        <v>122273721</v>
       </c>
       <c r="B19" t="n">
-        <v>95749</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,21 +2505,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571238</v>
+        <v>571172</v>
       </c>
       <c r="R19" t="n">
-        <v>6507436</v>
+        <v>6507239</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2646,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273731</v>
+        <v>122273727</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>98211</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,38 +2598,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571191</v>
+        <v>571200</v>
       </c>
       <c r="R20" t="n">
-        <v>6507391</v>
+        <v>6507458</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2730,6 +2677,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2748,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273728</v>
+        <v>122273722</v>
       </c>
       <c r="B21" t="n">
-        <v>91211</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2764,21 +2712,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
+        <v>106545</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571196</v>
+        <v>571231</v>
       </c>
       <c r="R21" t="n">
-        <v>6507330</v>
+        <v>6507251</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2850,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273727</v>
+        <v>122273726</v>
       </c>
       <c r="B22" t="n">
-        <v>98202</v>
+        <v>95800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,50 +2805,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>2590</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571200</v>
+        <v>571267</v>
       </c>
       <c r="R22" t="n">
-        <v>6507458</v>
+        <v>6507269</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2946,7 +2872,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2965,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273718</v>
+        <v>122273720</v>
       </c>
       <c r="B23" t="n">
-        <v>95749</v>
+        <v>90833</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2981,21 +2906,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +2925,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571268</v>
+        <v>571220</v>
       </c>
       <c r="R23" t="n">
-        <v>6507430</v>
+        <v>6507422</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282656</v>
+        <v>122282416</v>
       </c>
       <c r="B24" t="n">
-        <v>94867</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,37 +3003,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R24" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3187,11 +3112,6 @@
       <c r="E25" t="n">
         <v>100526</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Callidium coriaceum</t>
@@ -3276,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282416</v>
+        <v>122282656</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>94876</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3292,47 +3212,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>2170</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571210</v>
+        <v>571260</v>
       </c>
       <c r="R26" t="n">
-        <v>6507290</v>
+        <v>6507444</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3391,7 +3296,7 @@
         <v>122282513</v>
       </c>
       <c r="B27" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3405,11 +3310,6 @@
       </c>
       <c r="E27" t="n">
         <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3499,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282755</v>
+        <v>122282549</v>
       </c>
       <c r="B28" t="n">
-        <v>95749</v>
+        <v>95758</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3517,11 +3417,6 @@
       <c r="E28" t="n">
         <v>53</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Crossocalyx hellerianus</t>
@@ -3539,10 +3434,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571260</v>
+        <v>571228</v>
       </c>
       <c r="R28" t="n">
-        <v>6507444</v>
+        <v>6507441</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3601,10 +3496,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282433</v>
+        <v>122282755</v>
       </c>
       <c r="B29" t="n">
-        <v>94867</v>
+        <v>95758</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3613,25 +3508,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3641,13 +3531,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571196</v>
+        <v>571260</v>
       </c>
       <c r="R29" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3703,10 +3593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282549</v>
+        <v>122282433</v>
       </c>
       <c r="B30" t="n">
-        <v>95749</v>
+        <v>94876</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,25 +3605,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>2170</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3743,13 +3628,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571228</v>
+        <v>571196</v>
       </c>
       <c r="R30" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3690,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B31" t="n">
         <v>57532</v>
@@ -3823,11 +3708,6 @@
       <c r="E31" t="n">
         <v>103021</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -3838,29 +3718,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R31" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,19 +3779,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B32" t="n">
         <v>57532</v>
@@ -3937,11 +3809,6 @@
       <c r="E32" t="n">
         <v>103021</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -3952,21 +3819,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R32" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +3888,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273718</v>
+        <v>122273728</v>
       </c>
       <c r="B16" t="n">
-        <v>95758</v>
+        <v>91216</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5420</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571268</v>
+        <v>571196</v>
       </c>
       <c r="R16" t="n">
-        <v>6507430</v>
+        <v>6507330</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273717</v>
+        <v>122273721</v>
       </c>
       <c r="B17" t="n">
-        <v>95758</v>
+        <v>90833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571238</v>
+        <v>571172</v>
       </c>
       <c r="R17" t="n">
-        <v>6507436</v>
+        <v>6507239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273728</v>
+        <v>122273718</v>
       </c>
       <c r="B18" t="n">
-        <v>91216</v>
+        <v>95758</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,20 +2404,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571196</v>
+        <v>571268</v>
       </c>
       <c r="R18" t="n">
-        <v>6507330</v>
+        <v>6507430</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273721</v>
+        <v>122273717</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>95758</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,16 +2505,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571172</v>
+        <v>571238</v>
       </c>
       <c r="R19" t="n">
-        <v>6507239</v>
+        <v>6507436</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222306</v>
+        <v>122222234</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>105330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,30 +1324,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1359,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571205</v>
+        <v>571224</v>
       </c>
       <c r="R8" t="n">
-        <v>6507459</v>
+        <v>6507389</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222209</v>
+        <v>122222306</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,6 +1454,11 @@
       <c r="E9" t="n">
         <v>220787</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1461,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1478,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571189</v>
+        <v>571205</v>
       </c>
       <c r="R9" t="n">
-        <v>6507243</v>
+        <v>6507459</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222191</v>
+        <v>122222209</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,6 +1578,11 @@
       <c r="E10" t="n">
         <v>220787</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1580,7 +1595,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1597,14 +1612,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571216</v>
+        <v>571189</v>
       </c>
       <c r="R10" t="n">
-        <v>6507246</v>
+        <v>6507243</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222234</v>
+        <v>122222260</v>
       </c>
       <c r="B11" t="n">
-        <v>105317</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,30 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1716,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571224</v>
+        <v>571242</v>
       </c>
       <c r="R11" t="n">
-        <v>6507389</v>
+        <v>6507395</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1788,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222260</v>
+        <v>122222191</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,6 +1826,11 @@
       <c r="E12" t="n">
         <v>220787</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1818,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1835,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571242</v>
+        <v>571216</v>
       </c>
       <c r="R12" t="n">
-        <v>6507395</v>
+        <v>6507246</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1907,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273716</v>
+        <v>122273727</v>
       </c>
       <c r="B13" t="n">
-        <v>95758</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,33 +1944,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571230</v>
+        <v>571200</v>
       </c>
       <c r="R13" t="n">
-        <v>6507422</v>
+        <v>6507458</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1986,6 +2028,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273731</v>
+        <v>122273726</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>95813</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,16 +2063,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2590</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571191</v>
+        <v>571267</v>
       </c>
       <c r="R14" t="n">
-        <v>6507391</v>
+        <v>6507269</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2101,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273730</v>
+        <v>122273720</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,20 +2161,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571190</v>
+        <v>571220</v>
       </c>
       <c r="R15" t="n">
-        <v>6507410</v>
+        <v>6507422</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2198,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273728</v>
+        <v>122273717</v>
       </c>
       <c r="B16" t="n">
-        <v>91216</v>
+        <v>95771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,20 +2263,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571196</v>
+        <v>571238</v>
       </c>
       <c r="R16" t="n">
-        <v>6507330</v>
+        <v>6507436</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2295,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273721</v>
+        <v>122273722</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,20 +2365,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2393,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571172</v>
+        <v>571231</v>
       </c>
       <c r="R17" t="n">
-        <v>6507239</v>
+        <v>6507251</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2392,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273718</v>
+        <v>122273721</v>
       </c>
       <c r="B18" t="n">
-        <v>95758</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,16 +2471,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571268</v>
+        <v>571172</v>
       </c>
       <c r="R18" t="n">
-        <v>6507430</v>
+        <v>6507239</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2489,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273717</v>
+        <v>122273730</v>
       </c>
       <c r="B19" t="n">
-        <v>95758</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,20 +2569,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571238</v>
+        <v>571190</v>
       </c>
       <c r="R19" t="n">
-        <v>6507436</v>
+        <v>6507410</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273727</v>
+        <v>122273718</v>
       </c>
       <c r="B20" t="n">
-        <v>98211</v>
+        <v>95771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,45 +2671,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571200</v>
+        <v>571268</v>
       </c>
       <c r="R20" t="n">
-        <v>6507458</v>
+        <v>6507430</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2677,7 +2743,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2696,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273722</v>
+        <v>122273731</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,16 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2731,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571231</v>
+        <v>571191</v>
       </c>
       <c r="R21" t="n">
-        <v>6507251</v>
+        <v>6507391</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2793,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273726</v>
+        <v>122273728</v>
       </c>
       <c r="B22" t="n">
-        <v>95800</v>
+        <v>91229</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,16 +2879,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>5420</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2828,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571267</v>
+        <v>571196</v>
       </c>
       <c r="R22" t="n">
-        <v>6507269</v>
+        <v>6507330</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2890,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273720</v>
+        <v>122273716</v>
       </c>
       <c r="B23" t="n">
-        <v>90833</v>
+        <v>95771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,16 +2981,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>53</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2925,7 +3005,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571220</v>
+        <v>571230</v>
       </c>
       <c r="R23" t="n">
         <v>6507422</v>
@@ -3005,6 +3085,11 @@
       <c r="E24" t="n">
         <v>100526</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Callidium coriaceum</t>
@@ -3094,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282429</v>
+        <v>122282513</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>98224</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,26 +3191,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3134,13 +3228,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571198</v>
+        <v>571238</v>
       </c>
       <c r="R25" t="n">
-        <v>6507329</v>
+        <v>6507409</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3184,22 +3278,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282656</v>
+        <v>122282549</v>
       </c>
       <c r="B26" t="n">
-        <v>94876</v>
+        <v>95771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3208,20 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2170</v>
+        <v>53</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571260</v>
+        <v>571228</v>
       </c>
       <c r="R26" t="n">
-        <v>6507444</v>
+        <v>6507441</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3293,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282513</v>
+        <v>122282429</v>
       </c>
       <c r="B27" t="n">
-        <v>98211</v>
+        <v>5173</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3305,30 +3404,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3337,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571238</v>
+        <v>571198</v>
       </c>
       <c r="R27" t="n">
-        <v>6507409</v>
+        <v>6507329</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3387,22 +3487,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282549</v>
+        <v>122282433</v>
       </c>
       <c r="B28" t="n">
-        <v>95758</v>
+        <v>94889</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,20 +3511,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2170</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3434,13 +3539,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571228</v>
+        <v>571196</v>
       </c>
       <c r="R28" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3499,7 +3604,7 @@
         <v>122282755</v>
       </c>
       <c r="B29" t="n">
-        <v>95758</v>
+        <v>95771</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,6 +3618,11 @@
       </c>
       <c r="E29" t="n">
         <v>53</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3593,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282433</v>
+        <v>122282656</v>
       </c>
       <c r="B30" t="n">
-        <v>94876</v>
+        <v>94889</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3611,6 +3721,11 @@
       <c r="E30" t="n">
         <v>2170</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Dicranum flagellare</t>
@@ -3628,13 +3743,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571196</v>
+        <v>571260</v>
       </c>
       <c r="R30" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3693,7 +3808,7 @@
         <v>122296905</v>
       </c>
       <c r="B31" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3707,6 +3822,11 @@
       </c>
       <c r="E31" t="n">
         <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3794,7 +3914,7 @@
         <v>122297622</v>
       </c>
       <c r="B32" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3808,6 +3928,11 @@
       </c>
       <c r="E32" t="n">
         <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222234</v>
+        <v>122222306</v>
       </c>
       <c r="B8" t="n">
-        <v>105330</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,35 +1324,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571224</v>
+        <v>571205</v>
       </c>
       <c r="R8" t="n">
-        <v>6507389</v>
+        <v>6507459</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222306</v>
+        <v>122222191</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571205</v>
+        <v>571216</v>
       </c>
       <c r="R9" t="n">
-        <v>6507459</v>
+        <v>6507246</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222209</v>
+        <v>122222234</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>105343</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1612,14 +1612,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571189</v>
+        <v>571224</v>
       </c>
       <c r="R10" t="n">
-        <v>6507243</v>
+        <v>6507389</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1687,7 +1687,7 @@
         <v>122222260</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222191</v>
+        <v>122222209</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571216</v>
+        <v>571189</v>
       </c>
       <c r="R12" t="n">
-        <v>6507246</v>
+        <v>6507243</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273727</v>
+        <v>122273726</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>95826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,50 +1944,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571200</v>
+        <v>571267</v>
       </c>
       <c r="R13" t="n">
-        <v>6507458</v>
+        <v>6507269</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2028,7 +2016,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2047,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273726</v>
+        <v>122273716</v>
       </c>
       <c r="B14" t="n">
-        <v>95813</v>
+        <v>95784</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2087,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571267</v>
+        <v>571230</v>
       </c>
       <c r="R14" t="n">
-        <v>6507269</v>
+        <v>6507422</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2149,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273720</v>
+        <v>122273721</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571220</v>
+        <v>571172</v>
       </c>
       <c r="R15" t="n">
-        <v>6507422</v>
+        <v>6507239</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2251,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273717</v>
+        <v>122273728</v>
       </c>
       <c r="B16" t="n">
-        <v>95771</v>
+        <v>91242</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,25 +2250,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2291,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571238</v>
+        <v>571196</v>
       </c>
       <c r="R16" t="n">
-        <v>6507436</v>
+        <v>6507330</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2353,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273722</v>
+        <v>122273731</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2369,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571231</v>
+        <v>571191</v>
       </c>
       <c r="R17" t="n">
-        <v>6507251</v>
+        <v>6507391</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2455,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273721</v>
+        <v>122273722</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571172</v>
+        <v>571231</v>
       </c>
       <c r="R18" t="n">
-        <v>6507239</v>
+        <v>6507251</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2557,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273730</v>
+        <v>122273720</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>90859</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571190</v>
+        <v>571220</v>
       </c>
       <c r="R19" t="n">
-        <v>6507410</v>
+        <v>6507422</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2659,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273718</v>
+        <v>122273727</v>
       </c>
       <c r="B20" t="n">
-        <v>95771</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,38 +2658,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571268</v>
+        <v>571200</v>
       </c>
       <c r="R20" t="n">
-        <v>6507430</v>
+        <v>6507458</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2743,6 +2742,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273731</v>
+        <v>122273717</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>95784</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571191</v>
+        <v>571238</v>
       </c>
       <c r="R21" t="n">
-        <v>6507391</v>
+        <v>6507436</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273728</v>
+        <v>122273718</v>
       </c>
       <c r="B22" t="n">
-        <v>91229</v>
+        <v>95784</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,25 +2875,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571196</v>
+        <v>571268</v>
       </c>
       <c r="R22" t="n">
-        <v>6507330</v>
+        <v>6507430</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273716</v>
+        <v>122273730</v>
       </c>
       <c r="B23" t="n">
-        <v>95771</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,25 +2977,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571230</v>
+        <v>571190</v>
       </c>
       <c r="R23" t="n">
-        <v>6507422</v>
+        <v>6507410</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282416</v>
+        <v>122282513</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>98237</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,36 +3079,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571210</v>
+        <v>571238</v>
       </c>
       <c r="R24" t="n">
-        <v>6507290</v>
+        <v>6507409</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3167,22 +3166,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282513</v>
+        <v>122282549</v>
       </c>
       <c r="B25" t="n">
-        <v>98224</v>
+        <v>95784</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,50 +3190,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571238</v>
+        <v>571228</v>
       </c>
       <c r="R25" t="n">
-        <v>6507409</v>
+        <v>6507441</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3278,22 +3268,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282549</v>
+        <v>122282433</v>
       </c>
       <c r="B26" t="n">
-        <v>95771</v>
+        <v>94902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3292,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,13 +3320,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571228</v>
+        <v>571196</v>
       </c>
       <c r="R26" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3499,10 +3489,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282433</v>
+        <v>122282416</v>
       </c>
       <c r="B28" t="n">
-        <v>94889</v>
+        <v>5173</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,34 +3505,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571196</v>
+        <v>571210</v>
       </c>
       <c r="R28" t="n">
-        <v>6507329</v>
+        <v>6507290</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282755</v>
+        <v>122282656</v>
       </c>
       <c r="B29" t="n">
-        <v>95771</v>
+        <v>94902</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3613,25 +3613,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282656</v>
+        <v>122282755</v>
       </c>
       <c r="B30" t="n">
-        <v>94889</v>
+        <v>95784</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273722</v>
+        <v>122273720</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>90859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571231</v>
+        <v>571220</v>
       </c>
       <c r="R18" t="n">
-        <v>6507251</v>
+        <v>6507422</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273720</v>
+        <v>122273722</v>
       </c>
       <c r="B19" t="n">
-        <v>90859</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571220</v>
+        <v>571231</v>
       </c>
       <c r="R19" t="n">
-        <v>6507422</v>
+        <v>6507251</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222306</v>
+        <v>122222209</v>
       </c>
       <c r="B8" t="n">
         <v>98237</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571205</v>
+        <v>571189</v>
       </c>
       <c r="R8" t="n">
-        <v>6507459</v>
+        <v>6507243</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222191</v>
+        <v>122222260</v>
       </c>
       <c r="B9" t="n">
         <v>98237</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571216</v>
+        <v>571242</v>
       </c>
       <c r="R9" t="n">
-        <v>6507246</v>
+        <v>6507395</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222234</v>
+        <v>122222306</v>
       </c>
       <c r="B10" t="n">
-        <v>105343</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1612,14 +1612,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571224</v>
+        <v>571205</v>
       </c>
       <c r="R10" t="n">
-        <v>6507389</v>
+        <v>6507459</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222260</v>
+        <v>122222191</v>
       </c>
       <c r="B11" t="n">
         <v>98237</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571242</v>
+        <v>571216</v>
       </c>
       <c r="R11" t="n">
-        <v>6507395</v>
+        <v>6507246</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222209</v>
+        <v>122222234</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,35 +1820,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571189</v>
+        <v>571224</v>
       </c>
       <c r="R12" t="n">
-        <v>6507243</v>
+        <v>6507389</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273726</v>
+        <v>122273731</v>
       </c>
       <c r="B13" t="n">
-        <v>95826</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1948,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571267</v>
+        <v>571191</v>
       </c>
       <c r="R13" t="n">
-        <v>6507269</v>
+        <v>6507391</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273716</v>
+        <v>122273720</v>
       </c>
       <c r="B14" t="n">
-        <v>95784</v>
+        <v>90859</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571230</v>
+        <v>571220</v>
       </c>
       <c r="R14" t="n">
         <v>6507422</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273721</v>
+        <v>122273722</v>
       </c>
       <c r="B15" t="n">
-        <v>90859</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571172</v>
+        <v>571231</v>
       </c>
       <c r="R15" t="n">
-        <v>6507239</v>
+        <v>6507251</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273728</v>
+        <v>122273718</v>
       </c>
       <c r="B16" t="n">
-        <v>91242</v>
+        <v>95784</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,25 +2250,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571196</v>
+        <v>571268</v>
       </c>
       <c r="R16" t="n">
-        <v>6507330</v>
+        <v>6507430</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273731</v>
+        <v>122273728</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>91242</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571191</v>
+        <v>571196</v>
       </c>
       <c r="R17" t="n">
-        <v>6507391</v>
+        <v>6507330</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273720</v>
+        <v>122273727</v>
       </c>
       <c r="B18" t="n">
-        <v>90859</v>
+        <v>98237</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,38 +2454,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571220</v>
+        <v>571200</v>
       </c>
       <c r="R18" t="n">
-        <v>6507422</v>
+        <v>6507458</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2526,6 +2538,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2544,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273722</v>
+        <v>122273721</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>90859</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,25 +2569,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571231</v>
+        <v>571172</v>
       </c>
       <c r="R19" t="n">
-        <v>6507251</v>
+        <v>6507239</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2646,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273727</v>
+        <v>122273726</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>95826</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,50 +2671,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571200</v>
+        <v>571267</v>
       </c>
       <c r="R20" t="n">
-        <v>6507458</v>
+        <v>6507269</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2742,7 +2743,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273717</v>
+        <v>122273730</v>
       </c>
       <c r="B21" t="n">
-        <v>95784</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571238</v>
+        <v>571190</v>
       </c>
       <c r="R21" t="n">
-        <v>6507436</v>
+        <v>6507410</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273718</v>
+        <v>122273717</v>
       </c>
       <c r="B22" t="n">
         <v>95784</v>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571268</v>
+        <v>571238</v>
       </c>
       <c r="R22" t="n">
-        <v>6507430</v>
+        <v>6507436</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273730</v>
+        <v>122273716</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>95784</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,25 +2977,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571190</v>
+        <v>571230</v>
       </c>
       <c r="R23" t="n">
-        <v>6507410</v>
+        <v>6507422</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282513</v>
+        <v>122282549</v>
       </c>
       <c r="B24" t="n">
-        <v>98237</v>
+        <v>95784</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,50 +3079,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571238</v>
+        <v>571228</v>
       </c>
       <c r="R24" t="n">
-        <v>6507409</v>
+        <v>6507441</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3166,19 +3157,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282549</v>
+        <v>122282755</v>
       </c>
       <c r="B25" t="n">
         <v>95784</v>
@@ -3218,10 +3209,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571228</v>
+        <v>571260</v>
       </c>
       <c r="R25" t="n">
-        <v>6507441</v>
+        <v>6507444</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3489,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282416</v>
+        <v>122282513</v>
       </c>
       <c r="B28" t="n">
-        <v>5173</v>
+        <v>98237</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3501,36 +3492,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3539,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571210</v>
+        <v>571238</v>
       </c>
       <c r="R28" t="n">
-        <v>6507290</v>
+        <v>6507409</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3589,22 +3579,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282656</v>
+        <v>122282416</v>
       </c>
       <c r="B29" t="n">
-        <v>94902</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,37 +3607,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R29" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282755</v>
+        <v>122282656</v>
       </c>
       <c r="B30" t="n">
-        <v>95784</v>
+        <v>94902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B31" t="n">
         <v>57536</v>
@@ -3838,21 +3838,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R31" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,19 +3907,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B32" t="n">
         <v>57536</v>
@@ -3944,29 +3952,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R32" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -3591,10 +3591,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282416</v>
+        <v>122282656</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>94902</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3607,47 +3607,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571210</v>
+        <v>571260</v>
       </c>
       <c r="R29" t="n">
-        <v>6507290</v>
+        <v>6507444</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3703,10 +3693,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282656</v>
+        <v>122282416</v>
       </c>
       <c r="B30" t="n">
-        <v>94902</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3719,37 +3709,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R30" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222209</v>
+        <v>122222260</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,14 +1364,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571189</v>
+        <v>571242</v>
       </c>
       <c r="R8" t="n">
-        <v>6507243</v>
+        <v>6507395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222260</v>
+        <v>122222191</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,14 +1488,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571242</v>
+        <v>571216</v>
       </c>
       <c r="R9" t="n">
-        <v>6507395</v>
+        <v>6507246</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1563,7 @@
         <v>122222306</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222191</v>
+        <v>122222234</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>105346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,35 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1736,14 +1736,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Falkviken NO 965 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571216</v>
+        <v>571224</v>
       </c>
       <c r="R11" t="n">
-        <v>6507246</v>
+        <v>6507389</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222234</v>
+        <v>122222209</v>
       </c>
       <c r="B12" t="n">
-        <v>105343</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,35 +1820,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1860,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571224</v>
+        <v>571189</v>
       </c>
       <c r="R12" t="n">
-        <v>6507389</v>
+        <v>6507243</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273731</v>
+        <v>122273717</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>95786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571191</v>
+        <v>571238</v>
       </c>
       <c r="R13" t="n">
-        <v>6507391</v>
+        <v>6507436</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273720</v>
+        <v>122273718</v>
       </c>
       <c r="B14" t="n">
-        <v>90859</v>
+        <v>95786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571220</v>
+        <v>571268</v>
       </c>
       <c r="R14" t="n">
-        <v>6507422</v>
+        <v>6507430</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273722</v>
+        <v>122273726</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>95828</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571231</v>
+        <v>571267</v>
       </c>
       <c r="R15" t="n">
-        <v>6507251</v>
+        <v>6507269</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273718</v>
+        <v>122273727</v>
       </c>
       <c r="B16" t="n">
-        <v>95784</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,38 +2250,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571268</v>
+        <v>571200</v>
       </c>
       <c r="R16" t="n">
-        <v>6507430</v>
+        <v>6507458</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2322,6 +2334,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2343,7 +2356,7 @@
         <v>122273728</v>
       </c>
       <c r="B17" t="n">
-        <v>91242</v>
+        <v>91243</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273727</v>
+        <v>122273720</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>90853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,50 +2467,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571200</v>
+        <v>571220</v>
       </c>
       <c r="R18" t="n">
-        <v>6507458</v>
+        <v>6507422</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2538,7 +2539,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273721</v>
+        <v>122273731</v>
       </c>
       <c r="B19" t="n">
-        <v>90859</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,25 +2569,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571172</v>
+        <v>571191</v>
       </c>
       <c r="R19" t="n">
-        <v>6507239</v>
+        <v>6507391</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273726</v>
+        <v>122273721</v>
       </c>
       <c r="B20" t="n">
-        <v>95826</v>
+        <v>90853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,25 +2671,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571267</v>
+        <v>571172</v>
       </c>
       <c r="R20" t="n">
-        <v>6507269</v>
+        <v>6507239</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273730</v>
+        <v>122273722</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2777,21 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571190</v>
+        <v>571231</v>
       </c>
       <c r="R21" t="n">
-        <v>6507410</v>
+        <v>6507251</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273717</v>
+        <v>122273730</v>
       </c>
       <c r="B22" t="n">
-        <v>95784</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,25 +2875,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571238</v>
+        <v>571190</v>
       </c>
       <c r="R22" t="n">
-        <v>6507436</v>
+        <v>6507410</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2968,7 +2968,7 @@
         <v>122273716</v>
       </c>
       <c r="B23" t="n">
-        <v>95784</v>
+        <v>95786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282549</v>
+        <v>122282755</v>
       </c>
       <c r="B24" t="n">
-        <v>95784</v>
+        <v>95786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571228</v>
+        <v>571260</v>
       </c>
       <c r="R24" t="n">
-        <v>6507441</v>
+        <v>6507444</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282755</v>
+        <v>122282549</v>
       </c>
       <c r="B25" t="n">
-        <v>95784</v>
+        <v>95786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571260</v>
+        <v>571228</v>
       </c>
       <c r="R25" t="n">
-        <v>6507444</v>
+        <v>6507441</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282433</v>
+        <v>122282429</v>
       </c>
       <c r="B26" t="n">
-        <v>94902</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3287,37 +3287,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571196</v>
+        <v>571198</v>
       </c>
       <c r="R26" t="n">
         <v>6507329</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3373,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282429</v>
+        <v>122282513</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
+        <v>98240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3385,31 +3390,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3418,13 +3427,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571198</v>
+        <v>571238</v>
       </c>
       <c r="R27" t="n">
-        <v>6507329</v>
+        <v>6507409</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3468,22 +3477,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282513</v>
+        <v>122282433</v>
       </c>
       <c r="B28" t="n">
-        <v>98237</v>
+        <v>94904</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3492,47 +3501,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571238</v>
+        <v>571196</v>
       </c>
       <c r="R28" t="n">
-        <v>6507409</v>
+        <v>6507329</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3579,12 +3579,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3594,7 +3594,7 @@
         <v>122282656</v>
       </c>
       <c r="B29" t="n">
-        <v>94902</v>
+        <v>94904</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B31" t="n">
         <v>57536</v>
@@ -3838,29 +3838,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R31" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,19 +3899,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B32" t="n">
         <v>57536</v>
@@ -3952,21 +3944,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R32" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1932,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273717</v>
+        <v>122273716</v>
       </c>
       <c r="B13" t="n">
         <v>95786</v>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571238</v>
+        <v>571230</v>
       </c>
       <c r="R13" t="n">
-        <v>6507436</v>
+        <v>6507422</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273718</v>
+        <v>122273720</v>
       </c>
       <c r="B14" t="n">
-        <v>95786</v>
+        <v>90853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571268</v>
+        <v>571220</v>
       </c>
       <c r="R14" t="n">
-        <v>6507430</v>
+        <v>6507422</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273728</v>
+        <v>122273731</v>
       </c>
       <c r="B17" t="n">
-        <v>91243</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571196</v>
+        <v>571191</v>
       </c>
       <c r="R17" t="n">
-        <v>6507330</v>
+        <v>6507391</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273720</v>
+        <v>122273728</v>
       </c>
       <c r="B18" t="n">
-        <v>90853</v>
+        <v>91243</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,25 +2467,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571220</v>
+        <v>571196</v>
       </c>
       <c r="R18" t="n">
-        <v>6507422</v>
+        <v>6507330</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273731</v>
+        <v>122273722</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571191</v>
+        <v>571231</v>
       </c>
       <c r="R19" t="n">
-        <v>6507391</v>
+        <v>6507251</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273721</v>
+        <v>122273718</v>
       </c>
       <c r="B20" t="n">
-        <v>90853</v>
+        <v>95786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571172</v>
+        <v>571268</v>
       </c>
       <c r="R20" t="n">
-        <v>6507239</v>
+        <v>6507430</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273722</v>
+        <v>122273717</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>95786</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571231</v>
+        <v>571238</v>
       </c>
       <c r="R21" t="n">
-        <v>6507251</v>
+        <v>6507436</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273716</v>
+        <v>122273721</v>
       </c>
       <c r="B23" t="n">
-        <v>95786</v>
+        <v>90853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571230</v>
+        <v>571172</v>
       </c>
       <c r="R23" t="n">
-        <v>6507422</v>
+        <v>6507239</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282755</v>
+        <v>122282416</v>
       </c>
       <c r="B24" t="n">
-        <v>95786</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,41 +3079,51 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R24" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3169,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282549</v>
+        <v>122282429</v>
       </c>
       <c r="B25" t="n">
-        <v>95786</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3181,38 +3191,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571228</v>
+        <v>571198</v>
       </c>
       <c r="R25" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3271,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282429</v>
+        <v>122282513</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>98240</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,31 +3298,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3316,13 +3335,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571198</v>
+        <v>571238</v>
       </c>
       <c r="R26" t="n">
-        <v>6507329</v>
+        <v>6507409</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3366,22 +3385,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282513</v>
+        <v>122282433</v>
       </c>
       <c r="B27" t="n">
-        <v>98240</v>
+        <v>94904</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,47 +3409,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571238</v>
+        <v>571196</v>
       </c>
       <c r="R27" t="n">
-        <v>6507409</v>
+        <v>6507329</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3477,22 +3487,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282433</v>
+        <v>122282549</v>
       </c>
       <c r="B28" t="n">
-        <v>94904</v>
+        <v>95786</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3501,25 +3511,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3529,13 +3539,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571196</v>
+        <v>571228</v>
       </c>
       <c r="R28" t="n">
-        <v>6507329</v>
+        <v>6507441</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3591,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282656</v>
+        <v>122282755</v>
       </c>
       <c r="B29" t="n">
-        <v>94904</v>
+        <v>95786</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3603,25 +3613,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3693,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282416</v>
+        <v>122282656</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>94904</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3709,47 +3719,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571210</v>
+        <v>571260</v>
       </c>
       <c r="R30" t="n">
-        <v>6507290</v>
+        <v>6507444</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B31" t="n">
         <v>57536</v>
@@ -3838,21 +3838,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R31" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,19 +3907,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B32" t="n">
         <v>57536</v>
@@ -3944,29 +3952,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R32" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273716</v>
+        <v>122273718</v>
       </c>
       <c r="B13" t="n">
-        <v>95786</v>
+        <v>95787</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571230</v>
+        <v>571268</v>
       </c>
       <c r="R13" t="n">
-        <v>6507422</v>
+        <v>6507430</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273720</v>
+        <v>122273730</v>
       </c>
       <c r="B14" t="n">
-        <v>90853</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571220</v>
+        <v>571190</v>
       </c>
       <c r="R14" t="n">
-        <v>6507422</v>
+        <v>6507410</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273726</v>
+        <v>122273727</v>
       </c>
       <c r="B15" t="n">
-        <v>95828</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,38 +2148,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571267</v>
+        <v>571200</v>
       </c>
       <c r="R15" t="n">
-        <v>6507269</v>
+        <v>6507458</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2220,6 +2232,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2238,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273727</v>
+        <v>122273731</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>5173</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,50 +2263,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571200</v>
+        <v>571191</v>
       </c>
       <c r="R16" t="n">
-        <v>6507458</v>
+        <v>6507391</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2334,7 +2335,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273731</v>
+        <v>122273716</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>95787</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571191</v>
+        <v>571230</v>
       </c>
       <c r="R17" t="n">
-        <v>6507391</v>
+        <v>6507422</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273728</v>
+        <v>122273717</v>
       </c>
       <c r="B18" t="n">
-        <v>91243</v>
+        <v>95787</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,25 +2467,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571196</v>
+        <v>571238</v>
       </c>
       <c r="R18" t="n">
-        <v>6507330</v>
+        <v>6507436</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273722</v>
+        <v>122273728</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>91244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571231</v>
+        <v>571196</v>
       </c>
       <c r="R19" t="n">
-        <v>6507251</v>
+        <v>6507330</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273718</v>
+        <v>122273720</v>
       </c>
       <c r="B20" t="n">
-        <v>95786</v>
+        <v>90854</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571268</v>
+        <v>571220</v>
       </c>
       <c r="R20" t="n">
-        <v>6507430</v>
+        <v>6507422</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273717</v>
+        <v>122273721</v>
       </c>
       <c r="B21" t="n">
-        <v>95786</v>
+        <v>90854</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2777,21 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571238</v>
+        <v>571172</v>
       </c>
       <c r="R21" t="n">
-        <v>6507436</v>
+        <v>6507239</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273730</v>
+        <v>122273726</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>95829</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571190</v>
+        <v>571267</v>
       </c>
       <c r="R22" t="n">
-        <v>6507410</v>
+        <v>6507269</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273721</v>
+        <v>122273722</v>
       </c>
       <c r="B23" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,25 +2977,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571172</v>
+        <v>571231</v>
       </c>
       <c r="R23" t="n">
-        <v>6507239</v>
+        <v>6507251</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282416</v>
+        <v>122282656</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>94905</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,47 +3083,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571210</v>
+        <v>571260</v>
       </c>
       <c r="R24" t="n">
-        <v>6507290</v>
+        <v>6507444</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3179,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282429</v>
+        <v>122282549</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>95787</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,43 +3181,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571198</v>
+        <v>571228</v>
       </c>
       <c r="R25" t="n">
-        <v>6507329</v>
+        <v>6507441</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3286,10 +3271,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282513</v>
+        <v>122282755</v>
       </c>
       <c r="B26" t="n">
-        <v>98240</v>
+        <v>95787</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,50 +3283,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571238</v>
+        <v>571260</v>
       </c>
       <c r="R26" t="n">
-        <v>6507409</v>
+        <v>6507444</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3385,22 +3361,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282433</v>
+        <v>122282429</v>
       </c>
       <c r="B27" t="n">
-        <v>94904</v>
+        <v>5173</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3413,37 +3389,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571196</v>
+        <v>571198</v>
       </c>
       <c r="R27" t="n">
         <v>6507329</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3499,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282549</v>
+        <v>122282433</v>
       </c>
       <c r="B28" t="n">
-        <v>95786</v>
+        <v>94905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,25 +3492,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3539,13 +3520,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571228</v>
+        <v>571196</v>
       </c>
       <c r="R28" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3601,10 +3582,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282755</v>
+        <v>122282513</v>
       </c>
       <c r="B29" t="n">
-        <v>95786</v>
+        <v>98241</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3613,41 +3594,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571260</v>
+        <v>571238</v>
       </c>
       <c r="R29" t="n">
-        <v>6507444</v>
+        <v>6507409</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3691,22 +3681,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282656</v>
+        <v>122282416</v>
       </c>
       <c r="B30" t="n">
-        <v>94904</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3719,37 +3709,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R30" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>122297622</v>
       </c>
       <c r="B31" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>122296905</v>
       </c>
       <c r="B32" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282656</v>
+        <v>122282416</v>
       </c>
       <c r="B24" t="n">
-        <v>94905</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,37 +3083,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571260</v>
+        <v>571210</v>
       </c>
       <c r="R24" t="n">
-        <v>6507444</v>
+        <v>6507290</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3169,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282549</v>
+        <v>122282429</v>
       </c>
       <c r="B25" t="n">
-        <v>95787</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3181,38 +3191,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571228</v>
+        <v>571198</v>
       </c>
       <c r="R25" t="n">
-        <v>6507441</v>
+        <v>6507329</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3271,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282755</v>
+        <v>122282433</v>
       </c>
       <c r="B26" t="n">
-        <v>95787</v>
+        <v>94908</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,25 +3298,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3311,13 +3326,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571260</v>
+        <v>571196</v>
       </c>
       <c r="R26" t="n">
-        <v>6507444</v>
+        <v>6507329</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3373,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282429</v>
+        <v>122282656</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
+        <v>94908</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3389,39 +3404,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571198</v>
+        <v>571260</v>
       </c>
       <c r="R27" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3480,10 +3490,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282433</v>
+        <v>122282755</v>
       </c>
       <c r="B28" t="n">
-        <v>94905</v>
+        <v>95790</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3492,25 +3502,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3520,13 +3530,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571196</v>
+        <v>571260</v>
       </c>
       <c r="R28" t="n">
-        <v>6507329</v>
+        <v>6507444</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3582,10 +3592,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282513</v>
+        <v>122282549</v>
       </c>
       <c r="B29" t="n">
-        <v>98241</v>
+        <v>95790</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3594,50 +3604,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571238</v>
+        <v>571228</v>
       </c>
       <c r="R29" t="n">
-        <v>6507409</v>
+        <v>6507441</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3681,22 +3682,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282416</v>
+        <v>122282513</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>98244</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3705,36 +3706,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571210</v>
+        <v>571238</v>
       </c>
       <c r="R30" t="n">
-        <v>6507290</v>
+        <v>6507409</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3793,19 +3793,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B31" t="n">
         <v>57537</v>
@@ -3838,29 +3838,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R31" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,19 +3899,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B32" t="n">
         <v>57537</v>
@@ -3952,21 +3944,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R32" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -3805,7 +3805,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122296905</v>
+        <v>122297622</v>
       </c>
       <c r="B31" t="n">
         <v>57537</v>
@@ -3838,21 +3838,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571174</v>
+        <v>571190</v>
       </c>
       <c r="R31" t="n">
-        <v>6507323</v>
+        <v>6507321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,19 +3907,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122297622</v>
+        <v>122296905</v>
       </c>
       <c r="B32" t="n">
         <v>57537</v>
@@ -3944,29 +3952,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571190</v>
+        <v>571174</v>
       </c>
       <c r="R32" t="n">
-        <v>6507321</v>
+        <v>6507323</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4023,6 +4023,131 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129866806</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Falkviken NO 995 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>571240</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6507400</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>E-Nor-0891</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -4028,7 +4028,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>107522376</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571253.4093893191</v>
+        <v>571254</v>
       </c>
       <c r="R2" t="n">
-        <v>6507216.24772907</v>
+        <v>6507216</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2023-03-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>107522377</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571252.6255856436</v>
+        <v>571253</v>
       </c>
       <c r="R3" t="n">
-        <v>6507202.199516454</v>
+        <v>6507202</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +840,9 @@
           <t>2023-03-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115616423</v>
+        <v>115616415</v>
       </c>
       <c r="B4" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571205</v>
+        <v>571203</v>
       </c>
       <c r="R4" t="n">
-        <v>6507263</v>
+        <v>6507262</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -994,61 +959,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
+          <t>Marika Sjödin, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115616425</v>
+        <v>122273716</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bärsjöskogen, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571210</v>
+        <v>571230</v>
       </c>
       <c r="R5" t="n">
-        <v>6507268</v>
+        <v>6507422</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1075,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,57 +1056,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115616424</v>
+        <v>122273717</v>
       </c>
       <c r="B6" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bärsjöskogen, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571206</v>
+        <v>571238</v>
       </c>
       <c r="R6" t="n">
-        <v>6507262</v>
+        <v>6507436</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1153,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115616415</v>
+        <v>122273718</v>
       </c>
       <c r="B7" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bärsjöskogen, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571203</v>
+        <v>571268</v>
       </c>
       <c r="R7" t="n">
-        <v>6507262</v>
+        <v>6507430</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,76 +1250,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122222260</v>
+        <v>122282549</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falkviken NO 995 m, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571242</v>
+        <v>571228</v>
       </c>
       <c r="R8" t="n">
-        <v>6507395</v>
+        <v>6507441</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,93 +1336,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222191</v>
+        <v>122282755</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falkviken NO 865 m, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571216</v>
+        <v>571260</v>
       </c>
       <c r="R9" t="n">
-        <v>6507246</v>
+        <v>6507444</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,93 +1433,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122222306</v>
+        <v>122282433</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falkviken NO 1010 m, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571205</v>
+        <v>571196</v>
       </c>
       <c r="R10" t="n">
-        <v>6507459</v>
+        <v>6507329</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,39 +1530,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122222234</v>
+        <v>122282656</v>
       </c>
       <c r="B11" t="n">
-        <v>105346</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,53 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Falkviken NO 965 m, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571224</v>
+        <v>571260</v>
       </c>
       <c r="R11" t="n">
-        <v>6507389</v>
+        <v>6507444</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,93 +1627,66 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122222209</v>
+        <v>115616423</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falkviken NO 850 m, Ög</t>
+          <t>Bärsjöskogen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571189</v>
+        <v>571205</v>
       </c>
       <c r="R12" t="n">
-        <v>6507243</v>
+        <v>6507263</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,74 +1724,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Marika Sjödin, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122273718</v>
+        <v>115616424</v>
       </c>
       <c r="B13" t="n">
-        <v>95787</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Bärsjöskogen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571268</v>
+        <v>571206</v>
       </c>
       <c r="R13" t="n">
-        <v>6507430</v>
+        <v>6507262</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2002,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,22 +1832,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122273730</v>
+        <v>122273726</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571190</v>
+        <v>571267</v>
       </c>
       <c r="R14" t="n">
-        <v>6507410</v>
+        <v>6507269</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,62 +1936,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122273727</v>
+        <v>122273728</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571200</v>
+        <v>571196</v>
       </c>
       <c r="R15" t="n">
-        <v>6507458</v>
+        <v>6507330</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2232,7 +2015,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122273731</v>
+        <v>122273720</v>
       </c>
       <c r="B16" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2291,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571191</v>
+        <v>571220</v>
       </c>
       <c r="R16" t="n">
-        <v>6507391</v>
+        <v>6507422</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2353,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122273716</v>
+        <v>122273721</v>
       </c>
       <c r="B17" t="n">
-        <v>95787</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571230</v>
+        <v>571172</v>
       </c>
       <c r="R17" t="n">
-        <v>6507422</v>
+        <v>6507239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2455,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122273717</v>
+        <v>122273730</v>
       </c>
       <c r="B18" t="n">
-        <v>95787</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571238</v>
+        <v>571190</v>
       </c>
       <c r="R18" t="n">
-        <v>6507436</v>
+        <v>6507410</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2557,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122273728</v>
+        <v>122273731</v>
       </c>
       <c r="B19" t="n">
-        <v>91244</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571196</v>
+        <v>571191</v>
       </c>
       <c r="R19" t="n">
-        <v>6507330</v>
+        <v>6507391</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2659,50 +2421,55 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122273720</v>
+        <v>122282416</v>
       </c>
       <c r="B20" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571220</v>
+        <v>571210</v>
       </c>
       <c r="R20" t="n">
-        <v>6507422</v>
+        <v>6507290</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2729,12 +2496,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,65 +2516,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122273721</v>
+        <v>122282429</v>
       </c>
       <c r="B21" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571172</v>
+        <v>571198</v>
       </c>
       <c r="R21" t="n">
-        <v>6507239</v>
+        <v>6507329</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2831,12 +2598,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,62 +2618,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122273726</v>
+        <v>107120375</v>
       </c>
       <c r="B22" t="n">
-        <v>95829</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>sydväst om bärssjön, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571267</v>
+        <v>571266</v>
       </c>
       <c r="R22" t="n">
-        <v>6507269</v>
+        <v>6507184</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2933,12 +2695,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,65 +2715,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Axel Lindahl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Axel Lindahl, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122273722</v>
+        <v>122296905</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571231</v>
+        <v>571174</v>
       </c>
       <c r="R23" t="n">
-        <v>6507251</v>
+        <v>6507323</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,12 +2796,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,75 +2816,72 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Clas Tornefjell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122282416</v>
+        <v>122297622</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Svallberget, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571210</v>
+        <v>571190</v>
       </c>
       <c r="R24" t="n">
-        <v>6507290</v>
+        <v>6507321</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3147,12 +2905,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,27 +2925,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122282429</v>
+        <v>122273722</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3195,42 +2948,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571198</v>
+        <v>571231</v>
       </c>
       <c r="R25" t="n">
-        <v>6507329</v>
+        <v>6507251</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,12 +3002,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,62 +3022,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
           <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122282433</v>
+        <v>115616425</v>
       </c>
       <c r="B26" t="n">
-        <v>94908</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Bärsjöskogen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571196</v>
+        <v>571210</v>
       </c>
       <c r="R26" t="n">
-        <v>6507329</v>
+        <v>6507268</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3356,12 +3103,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,71 +3117,83 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Marika Sjödin, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122282656</v>
+        <v>122222191</v>
       </c>
       <c r="B27" t="n">
-        <v>94908</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Falkviken NO 865 m, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571260</v>
+        <v>571216</v>
       </c>
       <c r="R27" t="n">
-        <v>6507444</v>
+        <v>6507246</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3458,12 +3217,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,71 +3231,88 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122282755</v>
+        <v>122222209</v>
       </c>
       <c r="B28" t="n">
-        <v>95790</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Falkviken NO 850 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571260</v>
+        <v>571189</v>
       </c>
       <c r="R28" t="n">
-        <v>6507444</v>
+        <v>6507243</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3560,12 +3336,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,71 +3350,88 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122282549</v>
+        <v>122222260</v>
       </c>
       <c r="B29" t="n">
-        <v>95790</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Falkviken NO 995 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571228</v>
+        <v>571242</v>
       </c>
       <c r="R29" t="n">
-        <v>6507441</v>
+        <v>6507395</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3662,12 +3455,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,33 +3469,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122282513</v>
+        <v>122222306</v>
       </c>
       <c r="B30" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3729,27 +3523,34 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svallberget, Svallberget, Ög</t>
+          <t>Falkviken NO 1010 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571238</v>
+        <v>571205</v>
       </c>
       <c r="R30" t="n">
-        <v>6507409</v>
+        <v>6507459</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3773,12 +3574,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3787,83 +3588,84 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122297622</v>
+        <v>122273727</v>
       </c>
       <c r="B31" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svallberget, Nedre Glottern, Ög</t>
+          <t>Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571190</v>
+        <v>571200</v>
       </c>
       <c r="R31" t="n">
-        <v>6507321</v>
+        <v>6507458</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3887,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3901,75 +3703,76 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122296905</v>
+        <v>122282513</v>
       </c>
       <c r="B32" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Svallberget, Svallberget, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571174</v>
+        <v>571238</v>
       </c>
       <c r="R32" t="n">
-        <v>6507323</v>
+        <v>6507409</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,12 +3796,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4013,12 +3816,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Clas Tornefjell</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4028,7 +3831,7 @@
         <v>129866806</v>
       </c>
       <c r="B33" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,6 +3950,125 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122222234</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Falkviken NO 965 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>571224</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6507389</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60898-2024 artfynd.xlsx
+++ b/artfynd/A 60898-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107522376</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107522377</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115616415</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273717</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273718</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282549</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282755</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282433</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282656</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115616423</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115616424</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273726</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273728</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273720</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273721</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273730</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273731</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282416</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282429</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107120375</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2825,6 +2935,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122296905</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2934,6 +3049,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122297622</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3031,6 +3151,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273722</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3133,6 +3258,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115616425</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3252,6 +3382,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122222191</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3371,6 +3506,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122222209</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3490,6 +3630,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122222260</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122222306</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3719,6 +3869,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273727</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3825,6 +3980,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122282513</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3950,6 +4110,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866806</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4069,8 +4234,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122222234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>